--- a/output/graficos_dimensiones/comunal_o_ocup_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:54</t>
+    <t xml:space="preserve">2026-09-09 22:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:43</t>
+    <t xml:space="preserve">2026-09-18 10:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:05</t>
+    <t xml:space="preserve">2026-09-23 12:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:10</t>
+    <t xml:space="preserve">2026-10-02 13:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:43</t>
+    <t xml:space="preserve">2026-10-05 09:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
